--- a/Codebooks/Human Codebooks/content - cleaned/E - Content Analysis Codebook (cleaned) - Rohan.xlsx
+++ b/Codebooks/Human Codebooks/content - cleaned/E - Content Analysis Codebook (cleaned) - Rohan.xlsx
@@ -714,7 +714,7 @@
       <c r="O2" s="3" t="inlineStr"/>
       <c r="P2" s="3" t="inlineStr">
         <is>
-          <t>Men’s behavior, Kenyan or Nigerian political/social problems</t>
+          <t>Kenyan or Nigerian political/social problems, Men's behavior</t>
         </is>
       </c>
       <c r="Q2" s="3" t="inlineStr"/>
@@ -788,7 +788,7 @@
       </c>
       <c r="C3" s="3" t="inlineStr">
         <is>
-          <t>Take off time from chasing those cheques and reward yourself with some quality ALONE time. Get yourself regular medical check ups - there are several things we men need looked at. Find time to speak regularly to a therapist. Trust me you don’t want to be a statistic</t>
+          <t>Take off time from chasing those cheques and reward yourself with some quality ALONE time. Get yourself regular medical check ups - there are several things we men need looked at. Find time to speak regularly to a therapist. Trust me you don't want to be a statistic</t>
         </is>
       </c>
       <c r="D3" s="3" t="inlineStr">
@@ -837,7 +837,7 @@
       <c r="O3" s="3" t="inlineStr"/>
       <c r="P3" s="3" t="inlineStr">
         <is>
-          <t>Men’s behavior, Mental health/emotional struggle</t>
+          <t>Mental health/emotional struggle, Men's behavior</t>
         </is>
       </c>
       <c r="Q3" s="3" t="inlineStr"/>
@@ -853,7 +853,7 @@
       </c>
       <c r="T3" s="3" t="inlineStr">
         <is>
-          <t>Commentary/opinion, Advice/instruction</t>
+          <t>Advice/instruction, Commentary/opinion</t>
         </is>
       </c>
       <c r="U3" s="3" t="inlineStr"/>
@@ -935,7 +935,7 @@
       <c r="F4" s="3" t="inlineStr"/>
       <c r="G4" s="3" t="inlineStr">
         <is>
-          <t>Family/children, Gender issues, e.g. equality</t>
+          <t>Gender issues, e.g. equality, Family/children</t>
         </is>
       </c>
       <c r="H4" s="3" t="inlineStr"/>
@@ -990,7 +990,7 @@
       <c r="U4" s="3" t="inlineStr"/>
       <c r="V4" s="3" t="inlineStr">
         <is>
-          <t>Information seeking, Self expression/identity construction</t>
+          <t>Self expression/identity construction, Information seeking</t>
         </is>
       </c>
       <c r="W4" s="3" t="inlineStr">
@@ -1058,7 +1058,7 @@
       <c r="F5" s="3" t="inlineStr"/>
       <c r="G5" s="3" t="inlineStr">
         <is>
-          <t>Mental health, Social issues, e.g. corruption, Gender issues, e.g. equality</t>
+          <t>Social issues, e.g. corruption, Gender issues, e.g. equality, Mental health</t>
         </is>
       </c>
       <c r="H5" s="3" t="inlineStr"/>
@@ -1091,7 +1091,7 @@
       <c r="O5" s="3" t="inlineStr"/>
       <c r="P5" s="3" t="inlineStr">
         <is>
-          <t>Mental health/emotional struggle, Kenyan or Nigerian political/social problems, Men’s behavior</t>
+          <t>Kenyan or Nigerian political/social problems, Mental health/emotional struggle, Men's behavior</t>
         </is>
       </c>
       <c r="Q5" s="3" t="inlineStr"/>
@@ -1230,7 +1230,7 @@
       </c>
       <c r="T6" s="3" t="inlineStr">
         <is>
-          <t>Personal story, Commentary/opinion</t>
+          <t>Commentary/opinion, Personal story</t>
         </is>
       </c>
       <c r="U6" s="3" t="inlineStr"/>
@@ -1292,7 +1292,7 @@
       </c>
       <c r="C7" s="3" t="inlineStr">
         <is>
-          <t>Fellow Nigerian men PLEASE take care of your physical and mental health. You didn’t choose your gender or the label of PROVIDER so abeg no kill yourself</t>
+          <t>Fellow Nigerian men PLEASE take care of your physical and mental health. You didn't choose your gender or the label of PROVIDER so abeg no kill yourself</t>
         </is>
       </c>
       <c r="D7" s="3" t="inlineStr">
@@ -1308,7 +1308,7 @@
       <c r="F7" s="3" t="inlineStr"/>
       <c r="G7" s="3" t="inlineStr">
         <is>
-          <t>Mental health, Gender issues, e.g. equality</t>
+          <t>Gender issues, e.g. equality, Mental health</t>
         </is>
       </c>
       <c r="H7" s="3" t="inlineStr"/>
@@ -1359,7 +1359,7 @@
       <c r="U7" s="3" t="inlineStr"/>
       <c r="V7" s="3" t="inlineStr">
         <is>
-          <t>Information seeking, Self expression/identity construction</t>
+          <t>Self expression/identity construction, Information seeking</t>
         </is>
       </c>
       <c r="W7" s="3" t="inlineStr">
@@ -1435,7 +1435,7 @@
       <c r="F8" s="3" t="inlineStr"/>
       <c r="G8" s="3" t="inlineStr">
         <is>
-          <t>Money/status, Dating/marriage</t>
+          <t>Dating/marriage, Money/status</t>
         </is>
       </c>
       <c r="H8" s="3" t="inlineStr"/>
@@ -1480,13 +1480,13 @@
       <c r="S8" s="3" t="inlineStr"/>
       <c r="T8" s="3" t="inlineStr">
         <is>
-          <t>Personal story, Commentary/opinion</t>
+          <t>Commentary/opinion, Personal story</t>
         </is>
       </c>
       <c r="U8" s="3" t="inlineStr"/>
       <c r="V8" s="3" t="inlineStr">
         <is>
-          <t>Information seeking, Self expression/identity construction</t>
+          <t>Self expression/identity construction, Information seeking</t>
         </is>
       </c>
       <c r="W8" s="3" t="inlineStr">
@@ -1554,13 +1554,13 @@
       <c r="F9" s="3" t="inlineStr"/>
       <c r="G9" s="3" t="inlineStr">
         <is>
-          <t>Money/status, Family/children</t>
+          <t>Family/children, Money/status</t>
         </is>
       </c>
       <c r="H9" s="3" t="inlineStr"/>
       <c r="I9" s="3" t="inlineStr">
         <is>
-          <t>Commentary/reaction content, Interview/conversational content</t>
+          <t>Interview/conversational content, Commentary/reaction content</t>
         </is>
       </c>
       <c r="J9" s="3" t="inlineStr"/>
@@ -1587,7 +1587,7 @@
       <c r="O9" s="3" t="inlineStr"/>
       <c r="P9" s="3" t="inlineStr">
         <is>
-          <t>Economic/status pressure, Mental health/emotional struggle</t>
+          <t>Mental health/emotional struggle, Economic/status pressure</t>
         </is>
       </c>
       <c r="Q9" s="3" t="inlineStr"/>
@@ -1605,12 +1605,12 @@
       <c r="U9" s="3" t="inlineStr"/>
       <c r="V9" s="3" t="inlineStr">
         <is>
-          <t>Information seeking, Self expression/identity construction</t>
+          <t>Self expression/identity construction, Information seeking</t>
         </is>
       </c>
       <c r="W9" s="3" t="inlineStr">
         <is>
-          <t>Personal experience, Cultural/social observations</t>
+          <t>Cultural/social observations, Personal experience</t>
         </is>
       </c>
       <c r="X9" s="3" t="inlineStr"/>
@@ -1732,18 +1732,18 @@
       <c r="U10" s="3" t="inlineStr"/>
       <c r="V10" s="3" t="inlineStr">
         <is>
-          <t>Information seeking, Connection/social interaction</t>
+          <t>Connection/social interaction, Information seeking</t>
         </is>
       </c>
       <c r="W10" s="3" t="inlineStr">
         <is>
-          <t>Personal experience, Moral/religious claims</t>
+          <t>Moral/religious claims, Personal experience</t>
         </is>
       </c>
       <c r="X10" s="3" t="inlineStr"/>
       <c r="Y10" s="3" t="inlineStr">
         <is>
-          <t>Anecdotal examples, References religion/tradition</t>
+          <t>References religion/tradition, Anecdotal examples</t>
         </is>
       </c>
       <c r="Z10" s="3" t="inlineStr"/>
@@ -1927,7 +1927,7 @@
       <c r="F12" s="3" t="inlineStr"/>
       <c r="G12" s="3" t="inlineStr">
         <is>
-          <t>Money/status, Family/children</t>
+          <t>Family/children, Money/status</t>
         </is>
       </c>
       <c r="H12" s="3" t="inlineStr"/>
@@ -1960,7 +1960,7 @@
       <c r="O12" s="3" t="inlineStr"/>
       <c r="P12" s="3" t="inlineStr">
         <is>
-          <t>Economic/status pressure, Kenyan or Nigerian political/social problems</t>
+          <t>Kenyan or Nigerian political/social problems, Economic/status pressure</t>
         </is>
       </c>
       <c r="Q12" s="3" t="inlineStr"/>
@@ -1976,7 +1976,7 @@
       </c>
       <c r="T12" s="3" t="inlineStr">
         <is>
-          <t>Personal story, Commentary/opinion</t>
+          <t>Commentary/opinion, Personal story</t>
         </is>
       </c>
       <c r="U12" s="3" t="inlineStr"/>
@@ -1987,7 +1987,7 @@
       </c>
       <c r="W12" s="3" t="inlineStr">
         <is>
-          <t>Personal experience, Cultural/social observations</t>
+          <t>Cultural/social observations, Personal experience</t>
         </is>
       </c>
       <c r="X12" s="3" t="inlineStr"/>
@@ -2099,7 +2099,7 @@
       </c>
       <c r="T13" s="3" t="inlineStr">
         <is>
-          <t>Personal story, Commentary/opinion</t>
+          <t>Commentary/opinion, Personal story</t>
         </is>
       </c>
       <c r="U13" s="3" t="inlineStr"/>
@@ -2110,13 +2110,13 @@
       </c>
       <c r="W13" s="3" t="inlineStr">
         <is>
-          <t>Personal experience, Cultural/social observations</t>
+          <t>Cultural/social observations, Personal experience</t>
         </is>
       </c>
       <c r="X13" s="3" t="inlineStr"/>
       <c r="Y13" s="3" t="inlineStr">
         <is>
-          <t>Anecdotal examples, Presented as common sense</t>
+          <t>Presented as common sense, Anecdotal examples</t>
         </is>
       </c>
       <c r="Z13" s="3" t="inlineStr"/>
@@ -2206,7 +2206,7 @@
       <c r="O14" s="3" t="inlineStr"/>
       <c r="P14" s="3" t="inlineStr">
         <is>
-          <t>Men’s behavior, Economic/status pressure, Kenyan or Nigerian political/social problems</t>
+          <t>Kenyan or Nigerian political/social problems, Economic/status pressure, Men's behavior</t>
         </is>
       </c>
       <c r="Q14" s="3" t="inlineStr"/>
@@ -2224,7 +2224,7 @@
       <c r="U14" s="3" t="inlineStr"/>
       <c r="V14" s="3" t="inlineStr">
         <is>
-          <t>Information seeking, Self expression/identity construction</t>
+          <t>Self expression/identity construction, Information seeking</t>
         </is>
       </c>
       <c r="W14" s="3" t="inlineStr">
@@ -2292,7 +2292,7 @@
       <c r="F15" s="3" t="inlineStr"/>
       <c r="G15" s="3" t="inlineStr">
         <is>
-          <t>Dating/marriage, Money/status, Family/children</t>
+          <t>Dating/marriage, Family/children, Money/status</t>
         </is>
       </c>
       <c r="H15" s="3" t="inlineStr"/>
@@ -2325,7 +2325,7 @@
       <c r="O15" s="3" t="inlineStr"/>
       <c r="P15" s="3" t="inlineStr">
         <is>
-          <t>Men’s behavior, Economic/status pressure</t>
+          <t>Economic/status pressure, Men's behavior</t>
         </is>
       </c>
       <c r="Q15" s="3" t="inlineStr"/>
@@ -2347,7 +2347,7 @@
       <c r="U15" s="3" t="inlineStr"/>
       <c r="V15" s="3" t="inlineStr">
         <is>
-          <t>Information seeking, Self expression/identity construction</t>
+          <t>Self expression/identity construction, Information seeking</t>
         </is>
       </c>
       <c r="W15" s="3" t="inlineStr">
@@ -2389,7 +2389,7 @@
       </c>
       <c r="AF15" s="3" t="inlineStr">
         <is>
-          <t>Calls for men to follow more equitable gender norms</t>
+          <t>Other</t>
         </is>
       </c>
       <c r="AG15" s="3" t="inlineStr"/>
@@ -2452,7 +2452,7 @@
       <c r="O16" s="3" t="inlineStr"/>
       <c r="P16" s="3" t="inlineStr">
         <is>
-          <t>Men’s behavior, Mental health/emotional struggle</t>
+          <t>Mental health/emotional struggle, Men's behavior</t>
         </is>
       </c>
       <c r="Q16" s="3" t="inlineStr"/>
@@ -2470,7 +2470,7 @@
       <c r="U16" s="3" t="inlineStr"/>
       <c r="V16" s="3" t="inlineStr">
         <is>
-          <t>Information seeking, Self expression/identity construction</t>
+          <t>Self expression/identity construction, Information seeking</t>
         </is>
       </c>
       <c r="W16" s="3" t="inlineStr">
@@ -2575,7 +2575,7 @@
       <c r="O17" s="3" t="inlineStr"/>
       <c r="P17" s="3" t="inlineStr">
         <is>
-          <t>Men’s behavior</t>
+          <t>Men's behavior</t>
         </is>
       </c>
       <c r="Q17" s="3" t="inlineStr"/>
@@ -2712,7 +2712,7 @@
       <c r="U18" s="3" t="inlineStr"/>
       <c r="V18" s="3" t="inlineStr">
         <is>
-          <t>Information seeking, Self expression/identity construction</t>
+          <t>Self expression/identity construction, Information seeking</t>
         </is>
       </c>
       <c r="W18" s="3" t="inlineStr">
@@ -3069,7 +3069,7 @@
       <c r="U21" s="3" t="inlineStr"/>
       <c r="V21" s="3" t="inlineStr">
         <is>
-          <t>Information seeking, Connection/social interaction</t>
+          <t>Connection/social interaction, Information seeking</t>
         </is>
       </c>
       <c r="W21" s="3" t="inlineStr">
@@ -3188,7 +3188,7 @@
       <c r="U22" s="3" t="inlineStr"/>
       <c r="V22" s="3" t="inlineStr">
         <is>
-          <t>Information seeking, Self expression/identity construction</t>
+          <t>Self expression/identity construction, Information seeking</t>
         </is>
       </c>
       <c r="W22" s="3" t="inlineStr">
@@ -3301,13 +3301,13 @@
       <c r="S23" s="3" t="inlineStr"/>
       <c r="T23" s="3" t="inlineStr">
         <is>
-          <t>Commentary/opinion, Advice/instruction</t>
+          <t>Advice/instruction, Commentary/opinion</t>
         </is>
       </c>
       <c r="U23" s="3" t="inlineStr"/>
       <c r="V23" s="3" t="inlineStr">
         <is>
-          <t>Information seeking, Self expression/identity construction</t>
+          <t>Self expression/identity construction, Information seeking</t>
         </is>
       </c>
       <c r="W23" s="3" t="inlineStr">
@@ -3555,7 +3555,7 @@
       </c>
       <c r="T25" s="3" t="inlineStr">
         <is>
-          <t>Commentary/opinion, Advice/instruction</t>
+          <t>Advice/instruction, Commentary/opinion</t>
         </is>
       </c>
       <c r="U25" s="3" t="inlineStr"/>
@@ -3801,7 +3801,7 @@
       <c r="S27" s="3" t="inlineStr"/>
       <c r="T27" s="3" t="inlineStr">
         <is>
-          <t>Commentary/opinion, Advice/instruction</t>
+          <t>Advice/instruction, Commentary/opinion</t>
         </is>
       </c>
       <c r="U27" s="3" t="inlineStr"/>
@@ -3908,7 +3908,7 @@
       <c r="O28" s="3" t="inlineStr"/>
       <c r="P28" s="3" t="inlineStr">
         <is>
-          <t>Women/feminism, Economic/status pressure</t>
+          <t>Economic/status pressure, Women/feminism</t>
         </is>
       </c>
       <c r="Q28" s="3" t="inlineStr"/>
@@ -3926,7 +3926,7 @@
       <c r="U28" s="3" t="inlineStr"/>
       <c r="V28" s="3" t="inlineStr">
         <is>
-          <t>Information seeking, Self expression/identity construction</t>
+          <t>Self expression/identity construction, Information seeking</t>
         </is>
       </c>
       <c r="W28" s="3" t="inlineStr">
@@ -4277,7 +4277,7 @@
       <c r="O31" s="3" t="inlineStr"/>
       <c r="P31" s="3" t="inlineStr">
         <is>
-          <t>Men’s behavior</t>
+          <t>Men's behavior</t>
         </is>
       </c>
       <c r="Q31" s="3" t="inlineStr"/>
@@ -4295,7 +4295,7 @@
       <c r="U31" s="3" t="inlineStr"/>
       <c r="V31" s="3" t="inlineStr">
         <is>
-          <t>Information seeking, Self expression/identity construction</t>
+          <t>Self expression/identity construction, Information seeking</t>
         </is>
       </c>
       <c r="W31" s="3" t="inlineStr">
@@ -4418,7 +4418,7 @@
       <c r="U32" s="3" t="inlineStr"/>
       <c r="V32" s="3" t="inlineStr">
         <is>
-          <t>Information seeking, Self expression/identity construction</t>
+          <t>Self expression/identity construction, Information seeking</t>
         </is>
       </c>
       <c r="W32" s="3" t="inlineStr">
@@ -4767,7 +4767,7 @@
       <c r="U35" s="3" t="inlineStr"/>
       <c r="V35" s="3" t="inlineStr">
         <is>
-          <t>Information seeking, Self expression/identity construction</t>
+          <t>Self expression/identity construction, Information seeking</t>
         </is>
       </c>
       <c r="W35" s="3" t="inlineStr">
@@ -4888,7 +4888,7 @@
       </c>
       <c r="T36" s="3" t="inlineStr">
         <is>
-          <t>Commentary/opinion, Advice/instruction</t>
+          <t>Advice/instruction, Commentary/opinion</t>
         </is>
       </c>
       <c r="U36" s="3" t="inlineStr"/>
@@ -4966,7 +4966,7 @@
       <c r="F37" s="3" t="inlineStr"/>
       <c r="G37" s="3" t="inlineStr">
         <is>
-          <t>Dating/marriage, Gender issues, e.g. equality</t>
+          <t>Gender issues, e.g. equality, Dating/marriage</t>
         </is>
       </c>
       <c r="H37" s="3" t="inlineStr"/>
@@ -5089,7 +5089,7 @@
       <c r="F38" s="3" t="inlineStr"/>
       <c r="G38" s="3" t="inlineStr">
         <is>
-          <t>Dating/marriage, Gender issues, e.g. equality</t>
+          <t>Gender issues, e.g. equality, Dating/marriage</t>
         </is>
       </c>
       <c r="H38" s="3" t="inlineStr"/>
@@ -5273,7 +5273,7 @@
       </c>
       <c r="T39" s="3" t="inlineStr">
         <is>
-          <t>Commentary/opinion, Advice/instruction, Personal story</t>
+          <t>Advice/instruction, Commentary/opinion, Personal story</t>
         </is>
       </c>
       <c r="U39" s="3" t="inlineStr"/>
@@ -5396,7 +5396,7 @@
       </c>
       <c r="T40" s="3" t="inlineStr">
         <is>
-          <t>Commentary/opinion, Advice/instruction</t>
+          <t>Advice/instruction, Commentary/opinion</t>
         </is>
       </c>
       <c r="U40" s="3" t="inlineStr"/>
@@ -5856,12 +5856,12 @@
       <c r="U2" s="3" t="inlineStr"/>
       <c r="V2" s="3" t="inlineStr">
         <is>
-          <t>Information seeking, Self expression/identity construction</t>
+          <t>Self expression/identity construction, Information seeking</t>
         </is>
       </c>
       <c r="W2" s="3" t="inlineStr">
         <is>
-          <t>Personal experience, Cultural/social observations</t>
+          <t>Cultural/social observations, Personal experience</t>
         </is>
       </c>
       <c r="X2" s="3" t="inlineStr"/>
@@ -5973,7 +5973,7 @@
       </c>
       <c r="T3" s="3" t="inlineStr">
         <is>
-          <t>Personal story, Advice/instruction</t>
+          <t>Advice/instruction, Personal story</t>
         </is>
       </c>
       <c r="U3" s="3" t="inlineStr"/>
@@ -6088,7 +6088,7 @@
       <c r="O4" s="3" t="inlineStr"/>
       <c r="P4" s="3" t="inlineStr">
         <is>
-          <t>Economic/status pressure, Mental health/emotional struggle</t>
+          <t>Mental health/emotional struggle, Economic/status pressure</t>
         </is>
       </c>
       <c r="Q4" s="3" t="inlineStr"/>
@@ -6398,7 +6398,7 @@
       </c>
       <c r="AF6" s="3" t="inlineStr">
         <is>
-          <t>Calls for politicians or social figures to do something</t>
+          <t>Calls for political / social action</t>
         </is>
       </c>
       <c r="AG6" s="3" t="inlineStr"/>
@@ -6547,7 +6547,7 @@
       <c r="F8" s="3" t="inlineStr"/>
       <c r="G8" s="3" t="inlineStr">
         <is>
-          <t>Mental health, Social issues, e.g. corruption</t>
+          <t>Social issues, e.g. corruption, Mental health</t>
         </is>
       </c>
       <c r="H8" s="3" t="inlineStr"/>
@@ -6580,7 +6580,7 @@
       <c r="O8" s="3" t="inlineStr"/>
       <c r="P8" s="3" t="inlineStr">
         <is>
-          <t>Men’s behavior, Mental health/emotional struggle</t>
+          <t>Mental health/emotional struggle, Men's behavior</t>
         </is>
       </c>
       <c r="Q8" s="3" t="inlineStr"/>
@@ -6789,7 +6789,7 @@
       <c r="F10" s="3" t="inlineStr"/>
       <c r="G10" s="3" t="inlineStr">
         <is>
-          <t>Mental health, Social issues, e.g. corruption</t>
+          <t>Social issues, e.g. corruption, Mental health</t>
         </is>
       </c>
       <c r="H10" s="3" t="inlineStr"/>
@@ -6822,7 +6822,7 @@
       <c r="O10" s="3" t="inlineStr"/>
       <c r="P10" s="3" t="inlineStr">
         <is>
-          <t>Mental health/emotional struggle, Global political/social/cultural problems, Other</t>
+          <t>Global political/social/cultural problems, Mental health/emotional struggle, Other</t>
         </is>
       </c>
       <c r="Q10" s="3" t="inlineStr">
@@ -6844,7 +6844,7 @@
       <c r="U10" s="3" t="inlineStr"/>
       <c r="V10" s="3" t="inlineStr">
         <is>
-          <t>Connection/social interaction, Self expression/identity construction</t>
+          <t>Self expression/identity construction, Connection/social interaction</t>
         </is>
       </c>
       <c r="W10" s="3" t="inlineStr">
@@ -6953,7 +6953,7 @@
       <c r="O11" s="3" t="inlineStr"/>
       <c r="P11" s="3" t="inlineStr">
         <is>
-          <t>Global political/social/cultural problems, Men’s behavior, Mental health/emotional struggle</t>
+          <t>Global political/social/cultural problems, Mental health/emotional struggle, Men's behavior</t>
         </is>
       </c>
       <c r="Q11" s="3" t="inlineStr"/>
@@ -6971,7 +6971,7 @@
       <c r="U11" s="3" t="inlineStr"/>
       <c r="V11" s="3" t="inlineStr">
         <is>
-          <t>Connection/social interaction, Self expression/identity construction</t>
+          <t>Self expression/identity construction, Connection/social interaction</t>
         </is>
       </c>
       <c r="W11" s="3" t="inlineStr">
@@ -7039,7 +7039,7 @@
       <c r="F12" s="3" t="inlineStr"/>
       <c r="G12" s="3" t="inlineStr">
         <is>
-          <t>Gender issues, e.g. equality, Social issues, e.g. corruption</t>
+          <t>Social issues, e.g. corruption, Gender issues, e.g. equality</t>
         </is>
       </c>
       <c r="H12" s="3" t="inlineStr"/>
@@ -7132,7 +7132,7 @@
       </c>
       <c r="AF12" s="3" t="inlineStr">
         <is>
-          <t>Calls for politicians or social figures to do something</t>
+          <t>Calls for political / social action</t>
         </is>
       </c>
       <c r="AG12" s="3" t="inlineStr"/>
@@ -7166,7 +7166,7 @@
       <c r="F13" s="3" t="inlineStr"/>
       <c r="G13" s="3" t="inlineStr">
         <is>
-          <t>Family/children, Gender issues, e.g. equality, Money/status</t>
+          <t>Gender issues, e.g. equality, Family/children, Money/status</t>
         </is>
       </c>
       <c r="H13" s="3" t="inlineStr"/>
@@ -7199,7 +7199,7 @@
       <c r="O13" s="3" t="inlineStr"/>
       <c r="P13" s="3" t="inlineStr">
         <is>
-          <t>Kenyan or Nigerian political/social problems, Men’s behavior, Economic/status pressure</t>
+          <t>Kenyan or Nigerian political/social problems, Economic/status pressure, Men's behavior</t>
         </is>
       </c>
       <c r="Q13" s="3" t="inlineStr"/>
@@ -7289,7 +7289,7 @@
       <c r="F14" s="3" t="inlineStr"/>
       <c r="G14" s="3" t="inlineStr">
         <is>
-          <t>Family/children, Dating/marriage, Gender issues, e.g. equality</t>
+          <t>Gender issues, e.g. equality, Dating/marriage, Family/children</t>
         </is>
       </c>
       <c r="H14" s="3" t="inlineStr"/>
@@ -7322,7 +7322,7 @@
       <c r="O14" s="3" t="inlineStr"/>
       <c r="P14" s="3" t="inlineStr">
         <is>
-          <t>Women/feminism, Kenyan or Nigerian political/social problems</t>
+          <t>Kenyan or Nigerian political/social problems, Women/feminism</t>
         </is>
       </c>
       <c r="Q14" s="3" t="inlineStr"/>
@@ -7412,7 +7412,7 @@
       <c r="F15" s="3" t="inlineStr"/>
       <c r="G15" s="3" t="inlineStr">
         <is>
-          <t>Gender issues, e.g. equality, Social issues, e.g. corruption</t>
+          <t>Social issues, e.g. corruption, Gender issues, e.g. equality</t>
         </is>
       </c>
       <c r="H15" s="3" t="inlineStr"/>
@@ -7457,7 +7457,7 @@
       <c r="S15" s="3" t="inlineStr"/>
       <c r="T15" s="3" t="inlineStr">
         <is>
-          <t>News/telling facts, Commentary/opinion</t>
+          <t>Commentary/opinion, News/telling facts</t>
         </is>
       </c>
       <c r="U15" s="3" t="inlineStr"/>
@@ -7849,7 +7849,7 @@
       </c>
       <c r="W18" s="3" t="inlineStr">
         <is>
-          <t>Personal experience, Generalizations about men/women</t>
+          <t>Generalizations about men/women, Personal experience</t>
         </is>
       </c>
       <c r="X18" s="3" t="inlineStr"/>
@@ -8154,7 +8154,7 @@
       <c r="F21" s="3" t="inlineStr"/>
       <c r="G21" s="3" t="inlineStr">
         <is>
-          <t>Dating/marriage, Religion/morality</t>
+          <t>Religion/morality, Dating/marriage</t>
         </is>
       </c>
       <c r="H21" s="3" t="inlineStr"/>
@@ -8199,7 +8199,7 @@
       <c r="S21" s="3" t="inlineStr"/>
       <c r="T21" s="3" t="inlineStr">
         <is>
-          <t>Personal story, Commentary/opinion</t>
+          <t>Commentary/opinion, Personal story</t>
         </is>
       </c>
       <c r="U21" s="3" t="inlineStr"/>
@@ -8273,7 +8273,7 @@
       <c r="F22" s="3" t="inlineStr"/>
       <c r="G22" s="3" t="inlineStr">
         <is>
-          <t>Family/children, Gender issues, e.g. equality</t>
+          <t>Gender issues, e.g. equality, Family/children</t>
         </is>
       </c>
       <c r="H22" s="3" t="inlineStr"/>
@@ -8429,7 +8429,7 @@
       <c r="O23" s="3" t="inlineStr"/>
       <c r="P23" s="3" t="inlineStr">
         <is>
-          <t>Women/feminism, Kenyan or Nigerian political/social problems</t>
+          <t>Kenyan or Nigerian political/social problems, Women/feminism</t>
         </is>
       </c>
       <c r="Q23" s="3" t="inlineStr"/>
@@ -8447,7 +8447,7 @@
       <c r="U23" s="3" t="inlineStr"/>
       <c r="V23" s="3" t="inlineStr">
         <is>
-          <t>Information seeking, Self expression/identity construction</t>
+          <t>Self expression/identity construction, Information seeking</t>
         </is>
       </c>
       <c r="W23" s="3" t="inlineStr">
@@ -8523,7 +8523,7 @@
       </c>
       <c r="G24" s="3" t="inlineStr">
         <is>
-          <t>Dating/marriage, Religion/morality</t>
+          <t>Religion/morality, Dating/marriage</t>
         </is>
       </c>
       <c r="H24" s="3" t="inlineStr"/>
@@ -8556,7 +8556,7 @@
       <c r="O24" s="3" t="inlineStr"/>
       <c r="P24" s="3" t="inlineStr">
         <is>
-          <t>Women/feminism, Kenyan or Nigerian political/social problems</t>
+          <t>Kenyan or Nigerian political/social problems, Women/feminism</t>
         </is>
       </c>
       <c r="Q24" s="3" t="inlineStr"/>
@@ -8777,7 +8777,7 @@
       <c r="F26" s="3" t="inlineStr"/>
       <c r="G26" s="3" t="inlineStr">
         <is>
-          <t>Money/status, Dating/marriage</t>
+          <t>Dating/marriage, Money/status</t>
         </is>
       </c>
       <c r="H26" s="3" t="inlineStr"/>
@@ -8828,7 +8828,7 @@
       <c r="U26" s="3" t="inlineStr"/>
       <c r="V26" s="3" t="inlineStr">
         <is>
-          <t>Status seeking, Self expression/identity construction</t>
+          <t>Self expression/identity construction, Status seeking</t>
         </is>
       </c>
       <c r="W26" s="3" t="inlineStr">
@@ -8912,7 +8912,7 @@
       </c>
       <c r="G27" s="3" t="inlineStr">
         <is>
-          <t>Dating/marriage, Gender issues, e.g. equality</t>
+          <t>Gender issues, e.g. equality, Dating/marriage</t>
         </is>
       </c>
       <c r="H27" s="3" t="inlineStr"/>
@@ -9005,7 +9005,7 @@
       </c>
       <c r="AF27" s="3" t="inlineStr">
         <is>
-          <t>Calls for women to follow more traditional gender norm</t>
+          <t>Other</t>
         </is>
       </c>
       <c r="AG27" s="3" t="inlineStr"/>
@@ -9285,7 +9285,7 @@
       <c r="F30" s="3" t="inlineStr"/>
       <c r="G30" s="3" t="inlineStr">
         <is>
-          <t>Family/children, Dating/marriage</t>
+          <t>Dating/marriage, Family/children</t>
         </is>
       </c>
       <c r="H30" s="3" t="inlineStr"/>
@@ -9453,7 +9453,7 @@
       <c r="O31" s="3" t="inlineStr"/>
       <c r="P31" s="3" t="inlineStr">
         <is>
-          <t>Women/feminism, Men’s behavior</t>
+          <t>Women/feminism, Men's behavior</t>
         </is>
       </c>
       <c r="Q31" s="3" t="inlineStr"/>
@@ -9588,7 +9588,7 @@
       </c>
       <c r="P32" s="3" t="inlineStr">
         <is>
-          <t>Women/feminism, Men’s behavior</t>
+          <t>Women/feminism, Men's behavior</t>
         </is>
       </c>
       <c r="Q32" s="3" t="inlineStr"/>
@@ -9711,7 +9711,7 @@
       <c r="O33" s="3" t="inlineStr"/>
       <c r="P33" s="3" t="inlineStr">
         <is>
-          <t>Women/feminism, Men’s behavior</t>
+          <t>Women/feminism, Men's behavior</t>
         </is>
       </c>
       <c r="Q33" s="3" t="inlineStr"/>
@@ -9771,7 +9771,7 @@
       </c>
       <c r="AF33" s="3" t="inlineStr">
         <is>
-          <t>Calls for men to follow more traditional gender norms, Calls for women to follow more traditional gender norms</t>
+          <t>Other</t>
         </is>
       </c>
       <c r="AG33" s="3" t="inlineStr"/>
@@ -9834,7 +9834,7 @@
       <c r="O34" s="3" t="inlineStr"/>
       <c r="P34" s="3" t="inlineStr">
         <is>
-          <t>Men’s behavior, Mental health/emotional struggle</t>
+          <t>Mental health/emotional struggle, Men's behavior</t>
         </is>
       </c>
       <c r="Q34" s="3" t="inlineStr"/>
@@ -9920,7 +9920,7 @@
       <c r="F35" s="3" t="inlineStr"/>
       <c r="G35" s="3" t="inlineStr">
         <is>
-          <t>Family/children, Friends/socializing</t>
+          <t>Friends/socializing, Family/children</t>
         </is>
       </c>
       <c r="H35" s="3" t="inlineStr"/>
@@ -9953,7 +9953,7 @@
       <c r="O35" s="3" t="inlineStr"/>
       <c r="P35" s="3" t="inlineStr">
         <is>
-          <t>Mental health/emotional struggle, Kenyan or Nigerian political/social problems</t>
+          <t>Kenyan or Nigerian political/social problems, Mental health/emotional struggle</t>
         </is>
       </c>
       <c r="Q35" s="3" t="inlineStr"/>
@@ -10076,7 +10076,7 @@
       </c>
       <c r="P36" s="3" t="inlineStr">
         <is>
-          <t>Men’s behavior, Mental health/emotional struggle</t>
+          <t>Mental health/emotional struggle, Men's behavior</t>
         </is>
       </c>
       <c r="Q36" s="3" t="inlineStr"/>
@@ -10088,13 +10088,13 @@
       <c r="S36" s="3" t="inlineStr"/>
       <c r="T36" s="3" t="inlineStr">
         <is>
-          <t>Personal story, Motivational speech</t>
+          <t>Motivational speech, Personal story</t>
         </is>
       </c>
       <c r="U36" s="3" t="inlineStr"/>
       <c r="V36" s="3" t="inlineStr">
         <is>
-          <t>Connection/social interaction, Self expression/identity construction</t>
+          <t>Self expression/identity construction, Connection/social interaction</t>
         </is>
       </c>
       <c r="W36" s="3" t="inlineStr">
@@ -10217,7 +10217,7 @@
       <c r="U37" s="3" t="inlineStr"/>
       <c r="V37" s="3" t="inlineStr">
         <is>
-          <t>Information seeking, Self expression/identity construction</t>
+          <t>Self expression/identity construction, Information seeking</t>
         </is>
       </c>
       <c r="W37" s="3" t="inlineStr">
@@ -10344,7 +10344,7 @@
       <c r="U38" s="3" t="inlineStr"/>
       <c r="V38" s="3" t="inlineStr">
         <is>
-          <t>Information seeking, Self expression/identity construction</t>
+          <t>Self expression/identity construction, Information seeking</t>
         </is>
       </c>
       <c r="W38" s="3" t="inlineStr">
@@ -10449,7 +10449,7 @@
       <c r="O39" s="3" t="inlineStr"/>
       <c r="P39" s="3" t="inlineStr">
         <is>
-          <t>Men’s behavior</t>
+          <t>Men's behavior</t>
         </is>
       </c>
       <c r="Q39" s="3" t="inlineStr"/>
@@ -10461,7 +10461,7 @@
       <c r="S39" s="3" t="inlineStr"/>
       <c r="T39" s="3" t="inlineStr">
         <is>
-          <t>Personal story, Commentary/opinion</t>
+          <t>Commentary/opinion, Personal story</t>
         </is>
       </c>
       <c r="U39" s="3" t="inlineStr"/>
@@ -10472,7 +10472,7 @@
       </c>
       <c r="W39" s="3" t="inlineStr">
         <is>
-          <t>Personal experience, Generalizations about men/women</t>
+          <t>Generalizations about men/women, Personal experience</t>
         </is>
       </c>
       <c r="X39" s="3" t="inlineStr"/>
@@ -10576,7 +10576,7 @@
       <c r="O40" s="3" t="inlineStr"/>
       <c r="P40" s="3" t="inlineStr">
         <is>
-          <t>Men’s behavior</t>
+          <t>Men's behavior</t>
         </is>
       </c>
       <c r="Q40" s="3" t="inlineStr"/>
@@ -10699,7 +10699,7 @@
       <c r="O41" s="3" t="inlineStr"/>
       <c r="P41" s="3" t="inlineStr">
         <is>
-          <t>Men’s behavior, Mental health/emotional struggle</t>
+          <t>Mental health/emotional struggle, Men's behavior</t>
         </is>
       </c>
       <c r="Q41" s="3" t="inlineStr"/>
@@ -10711,7 +10711,7 @@
       <c r="S41" s="3" t="inlineStr"/>
       <c r="T41" s="3" t="inlineStr">
         <is>
-          <t>Personal story, Commentary/opinion</t>
+          <t>Commentary/opinion, Personal story</t>
         </is>
       </c>
       <c r="U41" s="3" t="inlineStr"/>

--- a/Codebooks/Human Codebooks/content - cleaned/E - Content Analysis Codebook (cleaned) - Rohan.xlsx
+++ b/Codebooks/Human Codebooks/content - cleaned/E - Content Analysis Codebook (cleaned) - Rohan.xlsx
@@ -2389,7 +2389,7 @@
       </c>
       <c r="AF15" s="3" t="inlineStr">
         <is>
-          <t>Other</t>
+          <t>Calls for men to follow more equitable gender norms</t>
         </is>
       </c>
       <c r="AG15" s="3" t="inlineStr"/>
@@ -9771,7 +9771,7 @@
       </c>
       <c r="AF33" s="3" t="inlineStr">
         <is>
-          <t>Other</t>
+          <t>Calls for men to follow more traditional gender norms, Calls for women to follow more traditional gender norms</t>
         </is>
       </c>
       <c r="AG33" s="3" t="inlineStr"/>

--- a/Codebooks/Human Codebooks/content - cleaned/E - Content Analysis Codebook (cleaned) - Rohan.xlsx
+++ b/Codebooks/Human Codebooks/content - cleaned/E - Content Analysis Codebook (cleaned) - Rohan.xlsx
@@ -450,42 +450,42 @@
   <dimension ref="A1:AG41"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="18" customWidth="1" min="1" max="1"/>
-    <col width="45" customWidth="1" min="2" max="2"/>
-    <col width="45" customWidth="1" min="3" max="3"/>
-    <col width="28" customWidth="1" min="4" max="4"/>
-    <col width="28" customWidth="1" min="5" max="5"/>
-    <col width="22" customWidth="1" min="6" max="6"/>
-    <col width="28" customWidth="1" min="7" max="7"/>
-    <col width="28" customWidth="1" min="8" max="8"/>
-    <col width="28" customWidth="1" min="9" max="9"/>
-    <col width="28" customWidth="1" min="10" max="10"/>
-    <col width="28" customWidth="1" min="11" max="11"/>
-    <col width="28" customWidth="1" min="12" max="12"/>
-    <col width="28" customWidth="1" min="13" max="13"/>
-    <col width="28" customWidth="1" min="14" max="14"/>
-    <col width="28" customWidth="1" min="15" max="15"/>
-    <col width="28" customWidth="1" min="16" max="16"/>
-    <col width="28" customWidth="1" min="17" max="17"/>
-    <col width="28" customWidth="1" min="18" max="18"/>
-    <col width="28" customWidth="1" min="19" max="19"/>
-    <col width="28" customWidth="1" min="20" max="20"/>
-    <col width="28" customWidth="1" min="21" max="21"/>
-    <col width="28" customWidth="1" min="22" max="22"/>
-    <col width="28" customWidth="1" min="23" max="23"/>
-    <col width="28" customWidth="1" min="24" max="24"/>
-    <col width="28" customWidth="1" min="25" max="25"/>
-    <col width="28" customWidth="1" min="26" max="26"/>
-    <col width="28" customWidth="1" min="27" max="27"/>
-    <col width="28" customWidth="1" min="28" max="28"/>
-    <col width="28" customWidth="1" min="29" max="29"/>
-    <col width="28" customWidth="1" min="30" max="30"/>
-    <col width="28" customWidth="1" min="31" max="31"/>
-    <col width="28" customWidth="1" min="32" max="32"/>
-    <col width="28" customWidth="1" min="33" max="33"/>
+    <col width="22" customWidth="1" min="1" max="1"/>
+    <col width="50" customWidth="1" min="2" max="2"/>
+    <col width="50" customWidth="1" min="3" max="3"/>
+    <col width="26" customWidth="1" min="4" max="4"/>
+    <col width="26" customWidth="1" min="5" max="5"/>
+    <col width="26" customWidth="1" min="6" max="6"/>
+    <col width="26" customWidth="1" min="7" max="7"/>
+    <col width="26" customWidth="1" min="8" max="8"/>
+    <col width="26" customWidth="1" min="9" max="9"/>
+    <col width="26" customWidth="1" min="10" max="10"/>
+    <col width="26" customWidth="1" min="11" max="11"/>
+    <col width="26" customWidth="1" min="12" max="12"/>
+    <col width="26" customWidth="1" min="13" max="13"/>
+    <col width="26" customWidth="1" min="14" max="14"/>
+    <col width="26" customWidth="1" min="15" max="15"/>
+    <col width="26" customWidth="1" min="16" max="16"/>
+    <col width="26" customWidth="1" min="17" max="17"/>
+    <col width="26" customWidth="1" min="18" max="18"/>
+    <col width="26" customWidth="1" min="19" max="19"/>
+    <col width="26" customWidth="1" min="20" max="20"/>
+    <col width="26" customWidth="1" min="21" max="21"/>
+    <col width="26" customWidth="1" min="22" max="22"/>
+    <col width="26" customWidth="1" min="23" max="23"/>
+    <col width="26" customWidth="1" min="24" max="24"/>
+    <col width="26" customWidth="1" min="25" max="25"/>
+    <col width="26" customWidth="1" min="26" max="26"/>
+    <col width="26" customWidth="1" min="27" max="27"/>
+    <col width="26" customWidth="1" min="28" max="28"/>
+    <col width="26" customWidth="1" min="29" max="29"/>
+    <col width="26" customWidth="1" min="30" max="30"/>
+    <col width="26" customWidth="1" min="31" max="31"/>
+    <col width="26" customWidth="1" min="32" max="32"/>
+    <col width="26" customWidth="1" min="33" max="33"/>
   </cols>
   <sheetData>
-    <row r="1" ht="60" customHeight="1">
+    <row r="1" ht="48" customHeight="1">
       <c r="A1" s="2" t="inlineStr">
         <is>
           <t>Content ID</t>
@@ -5578,42 +5578,42 @@
   <dimension ref="A1:AG41"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="18" customWidth="1" min="1" max="1"/>
-    <col width="45" customWidth="1" min="2" max="2"/>
-    <col width="45" customWidth="1" min="3" max="3"/>
-    <col width="28" customWidth="1" min="4" max="4"/>
-    <col width="28" customWidth="1" min="5" max="5"/>
-    <col width="22" customWidth="1" min="6" max="6"/>
-    <col width="28" customWidth="1" min="7" max="7"/>
-    <col width="28" customWidth="1" min="8" max="8"/>
-    <col width="28" customWidth="1" min="9" max="9"/>
-    <col width="28" customWidth="1" min="10" max="10"/>
-    <col width="28" customWidth="1" min="11" max="11"/>
-    <col width="28" customWidth="1" min="12" max="12"/>
-    <col width="28" customWidth="1" min="13" max="13"/>
-    <col width="28" customWidth="1" min="14" max="14"/>
-    <col width="28" customWidth="1" min="15" max="15"/>
-    <col width="28" customWidth="1" min="16" max="16"/>
-    <col width="28" customWidth="1" min="17" max="17"/>
-    <col width="28" customWidth="1" min="18" max="18"/>
-    <col width="28" customWidth="1" min="19" max="19"/>
-    <col width="28" customWidth="1" min="20" max="20"/>
-    <col width="28" customWidth="1" min="21" max="21"/>
-    <col width="28" customWidth="1" min="22" max="22"/>
-    <col width="28" customWidth="1" min="23" max="23"/>
-    <col width="28" customWidth="1" min="24" max="24"/>
-    <col width="28" customWidth="1" min="25" max="25"/>
-    <col width="28" customWidth="1" min="26" max="26"/>
-    <col width="28" customWidth="1" min="27" max="27"/>
-    <col width="28" customWidth="1" min="28" max="28"/>
-    <col width="28" customWidth="1" min="29" max="29"/>
-    <col width="28" customWidth="1" min="30" max="30"/>
-    <col width="28" customWidth="1" min="31" max="31"/>
-    <col width="28" customWidth="1" min="32" max="32"/>
-    <col width="28" customWidth="1" min="33" max="33"/>
+    <col width="22" customWidth="1" min="1" max="1"/>
+    <col width="50" customWidth="1" min="2" max="2"/>
+    <col width="50" customWidth="1" min="3" max="3"/>
+    <col width="26" customWidth="1" min="4" max="4"/>
+    <col width="26" customWidth="1" min="5" max="5"/>
+    <col width="26" customWidth="1" min="6" max="6"/>
+    <col width="26" customWidth="1" min="7" max="7"/>
+    <col width="26" customWidth="1" min="8" max="8"/>
+    <col width="26" customWidth="1" min="9" max="9"/>
+    <col width="26" customWidth="1" min="10" max="10"/>
+    <col width="26" customWidth="1" min="11" max="11"/>
+    <col width="26" customWidth="1" min="12" max="12"/>
+    <col width="26" customWidth="1" min="13" max="13"/>
+    <col width="26" customWidth="1" min="14" max="14"/>
+    <col width="26" customWidth="1" min="15" max="15"/>
+    <col width="26" customWidth="1" min="16" max="16"/>
+    <col width="26" customWidth="1" min="17" max="17"/>
+    <col width="26" customWidth="1" min="18" max="18"/>
+    <col width="26" customWidth="1" min="19" max="19"/>
+    <col width="26" customWidth="1" min="20" max="20"/>
+    <col width="26" customWidth="1" min="21" max="21"/>
+    <col width="26" customWidth="1" min="22" max="22"/>
+    <col width="26" customWidth="1" min="23" max="23"/>
+    <col width="26" customWidth="1" min="24" max="24"/>
+    <col width="26" customWidth="1" min="25" max="25"/>
+    <col width="26" customWidth="1" min="26" max="26"/>
+    <col width="26" customWidth="1" min="27" max="27"/>
+    <col width="26" customWidth="1" min="28" max="28"/>
+    <col width="26" customWidth="1" min="29" max="29"/>
+    <col width="26" customWidth="1" min="30" max="30"/>
+    <col width="26" customWidth="1" min="31" max="31"/>
+    <col width="26" customWidth="1" min="32" max="32"/>
+    <col width="26" customWidth="1" min="33" max="33"/>
   </cols>
   <sheetData>
-    <row r="1" ht="60" customHeight="1">
+    <row r="1" ht="48" customHeight="1">
       <c r="A1" s="2" t="inlineStr">
         <is>
           <t>Content ID</t>
@@ -9005,7 +9005,7 @@
       </c>
       <c r="AF27" s="3" t="inlineStr">
         <is>
-          <t>Other</t>
+          <t>Calls for women to follow more traditional gender norm</t>
         </is>
       </c>
       <c r="AG27" s="3" t="inlineStr"/>
